--- a/data/trans_dic/P79$hipoteca_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P79$hipoteca_2023-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,91</t>
+          <t>0,0; 0,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,87</t>
+          <t>0,09; 0,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,67</t>
+          <t>0,07; 0,61</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,27</t>
+          <t>0,3; 1,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,38</t>
+          <t>0,38; 1,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,03</t>
+          <t>0,39; 1,19</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,72</t>
+          <t>0,35; 2,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,05</t>
+          <t>0,31; 1,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,06</t>
+          <t>0,44; 1,39</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,11</t>
+          <t>1,2; 3,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,61</t>
+          <t>0,51; 1,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,09</t>
+          <t>0,97; 1,93</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,29</t>
+          <t>0,69; 1,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,91</t>
+          <t>0,51; 0,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,0</t>
+          <t>0,66; 1,11</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>2233</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>3421</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5616</t>
+          <t>0; 5446</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>528; 6108</t>
+          <t>617; 6140</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1119; 8878</t>
+          <t>930; 8499</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>6650</t>
+          <t>7441</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7190</t>
+          <t>7908</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13840</t>
+          <t>15349</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2323; 14832</t>
+          <t>3109; 14616</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3572; 12683</t>
+          <t>3905; 14270</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7969; 21521</t>
+          <t>7998; 24432</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>7222</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9363</t>
+          <t>12663</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1696; 11647</t>
+          <t>2688; 15749</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1332; 9482</t>
+          <t>2430; 11166</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4771; 16831</t>
+          <t>6874; 21415</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>18021</t>
+          <t>18891</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9248</t>
+          <t>9916</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>28807</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10328; 27915</t>
+          <t>11491; 30482</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5120; 15891</t>
+          <t>5471; 16790</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18624; 39470</t>
+          <t>19790; 39272</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>30787</t>
+          <t>34742</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>22913</t>
+          <t>25499</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>53701</t>
+          <t>60241</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>19735; 43492</t>
+          <t>23716; 48897</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15615; 31908</t>
+          <t>18330; 35539</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>40136; 68994</t>
+          <t>46623; 77646</t>
         </is>
       </c>
     </row>
